--- a/EWY_US_Vektorium Master_20250901_20260501_graph.xlsx
+++ b/EWY_US_Vektorium Master_20250901_20260501_graph.xlsx
@@ -68,7 +68,7 @@
       <xdr:col>29</xdr:col>
       <xdr:colOff>529549</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>150890</xdr:rowOff>
+      <xdr:rowOff>138088</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -86,7 +86,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="17779324" cy="7008890"/>
+          <a:ext cx="17779324" cy="6996088"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
